--- a/KURIKULUM2026_REVISI/041_LAMPIRAN_BARU_BUKU_KPT.xlsx
+++ b/KURIKULUM2026_REVISI/041_LAMPIRAN_BARU_BUKU_KPT.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>STI-624 Integrasi AI [3] · STI-625 Smart City [2] · STI-626 Deep Learning [3] · STI-627 Platform Eng [3] · FST-611 Metopel [2] · MK Pilihan 2 &amp; 3 [3+3]</t>
+          <t>STI-726 Integrasi AI [3] · STI-727 Smart City [2] · STI-726 Deep Learning [3] · STI-727 Platform Eng [3] · FST-611 Metopel [2] · MK Pilihan 2 &amp; 3 [3+3]</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
